--- a/upload/baselegal_isencao.xlsx
+++ b/upload/baselegal_isencao.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
   <si>
     <t>Norma</t>
   </si>
@@ -615,109 +615,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -731,6 +656,75 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1022,306 +1016,346 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
     </row>
     <row r="2" spans="1:3" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="20"/>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="C2" s="24"/>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="4"/>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="5" t="s">
+      <c r="C3" s="26"/>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="6"/>
-    </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="5" t="s">
+      <c r="C4" s="18"/>
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="6"/>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="5" t="s">
+      <c r="C5" s="18"/>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="6"/>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="5" t="s">
+      <c r="C6" s="18"/>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="6"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="5" t="s">
+      <c r="C7" s="18"/>
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="6"/>
-    </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
-      <c r="B9" s="5" t="s">
+      <c r="C8" s="18"/>
+    </row>
+    <row r="9" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="6"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="5" t="s">
+      <c r="C9" s="18"/>
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="6"/>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="5" t="s">
+      <c r="C10" s="18"/>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="6"/>
-    </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="5" t="s">
+      <c r="C11" s="18"/>
+    </row>
+    <row r="12" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="6"/>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="5" t="s">
+      <c r="C12" s="18"/>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="6"/>
-    </row>
-    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
-      <c r="B14" s="5" t="s">
+      <c r="C13" s="18"/>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="6"/>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="5" t="s">
+      <c r="C14" s="18"/>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="6"/>
+      <c r="C15" s="18"/>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="12"/>
-      <c r="B16" s="7" t="s">
+      <c r="A16" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="8"/>
+      <c r="C16" s="20"/>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="23"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="26"/>
+      <c r="C18" s="34"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="16"/>
+      <c r="C19" s="36"/>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="15"/>
+      <c r="C20" s="38"/>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="16"/>
+      <c r="C21" s="36"/>
     </row>
     <row r="22" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="31"/>
+      <c r="C22" s="30"/>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="34"/>
+      <c r="C23" s="32"/>
     </row>
     <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="35" t="s">
+      <c r="B24" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="35" t="s">
+      <c r="C24" s="10" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="37" t="s">
+      <c r="B25" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="C25" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="10" t="s">
+    <row r="27" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="39"/>
+      <c r="B27" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="11"/>
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="11"/>
-      <c r="B29" s="35" t="s">
+    <row r="29" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="11"/>
-      <c r="B30" s="35" t="s">
+    <row r="30" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="11"/>
-      <c r="B31" s="35" t="s">
+    <row r="31" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="11"/>
-      <c r="B32" s="35" t="s">
+    <row r="32" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="11"/>
-      <c r="B33" s="35" t="s">
+    <row r="33" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="12"/>
-      <c r="B34" s="39" t="s">
+    <row r="34" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="41" t="s">
+      <c r="C34" s="16" t="s">
         <v>55</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="A27:A34"/>
-    <mergeCell ref="A3:A16"/>
+  <mergeCells count="23">
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
@@ -1330,10 +1364,6 @@
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C28" r:id="rId1" location="parte1it161"/>
